--- a/backend/order/src/test/resources/workbooks/DS-ORDER-3X/weekly/실리콘 02월 1주차 주간 계획.xlsx
+++ b/backend/order/src/test/resources/workbooks/DS-ORDER-3X/weekly/실리콘 02월 1주차 주간 계획.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:D61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,27 +424,17 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>수량</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>납기</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Fri</t>
+          <t>주차</t>
         </is>
       </c>
     </row>
@@ -465,21 +455,15 @@
       <c r="D2" t="n">
         <v>235</v>
       </c>
-      <c r="E2" t="n">
-        <v>471</v>
-      </c>
-      <c r="F2" t="n">
-        <v>39</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>29673-2F910</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>599</v>
+        <v>892</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -487,23 +471,17 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>219</v>
-      </c>
-      <c r="E3" t="n">
-        <v>293</v>
-      </c>
-      <c r="F3" t="n">
-        <v>207</v>
+        <v>160</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>28674-L5500</t>
+          <t>A6722031002</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>665</v>
+        <v>449</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -511,13 +489,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>213</v>
-      </c>
-      <c r="E4" t="n">
-        <v>148</v>
-      </c>
-      <c r="F4" t="n">
-        <v>58</v>
+        <v>293</v>
       </c>
     </row>
     <row r="5">
@@ -527,7 +499,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31</v>
+        <v>736</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -535,23 +507,17 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>494</v>
-      </c>
-      <c r="E5" t="n">
-        <v>166</v>
-      </c>
-      <c r="F5" t="n">
-        <v>87</v>
+        <v>327</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>25450-P7200</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>481</v>
+        <v>306</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -559,23 +525,17 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>425</v>
-      </c>
-      <c r="E6" t="n">
-        <v>353</v>
-      </c>
-      <c r="F6" t="n">
-        <v>470</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>25450-P7200</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>100</v>
+        <v>31</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -583,23 +543,17 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>223</v>
-      </c>
-      <c r="E7" t="n">
-        <v>432</v>
-      </c>
-      <c r="F7" t="n">
-        <v>54</v>
+        <v>494</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>28422-2M100</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>456</v>
+        <v>185</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -607,23 +561,17 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>301</v>
-      </c>
-      <c r="E8" t="n">
-        <v>205</v>
-      </c>
-      <c r="F8" t="n">
-        <v>268</v>
+        <v>410</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>A6722031002</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>415</v>
+        <v>481</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -631,23 +579,17 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>445</v>
-      </c>
-      <c r="E9" t="n">
-        <v>158</v>
-      </c>
-      <c r="F9" t="n">
-        <v>381</v>
+        <v>425</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>236</v>
+        <v>951</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -655,13 +597,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>170</v>
-      </c>
-      <c r="E10" t="n">
-        <v>398</v>
-      </c>
-      <c r="F10" t="n">
-        <v>86</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11">
@@ -671,7 +607,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>532</v>
+        <v>457</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -679,23 +615,17 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>324</v>
-      </c>
-      <c r="E11" t="n">
-        <v>58</v>
-      </c>
-      <c r="F11" t="n">
-        <v>271</v>
+        <v>432</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A6722030900</t>
+          <t>29673-2F910</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>208</v>
+        <v>259</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -703,23 +633,17 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>463</v>
-      </c>
-      <c r="E12" t="n">
-        <v>397</v>
-      </c>
-      <c r="F12" t="n">
-        <v>178</v>
+        <v>223</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>A6722031002</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>754</v>
+        <v>420</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -727,23 +651,17 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>490</v>
-      </c>
-      <c r="E13" t="n">
-        <v>419</v>
-      </c>
-      <c r="F13" t="n">
-        <v>330</v>
+        <v>268</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>29673-2R060</t>
+          <t>29673-2F910</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>251</v>
+        <v>415</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -751,23 +669,17 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>52</v>
-      </c>
-      <c r="E14" t="n">
-        <v>74</v>
-      </c>
-      <c r="F14" t="n">
-        <v>131</v>
+        <v>445</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>28421-2M100</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>187</v>
+        <v>773</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -775,23 +687,17 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>308</v>
-      </c>
-      <c r="E15" t="n">
-        <v>78</v>
-      </c>
-      <c r="F15" t="n">
-        <v>389</v>
+        <v>173</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>28415-08400</t>
+          <t>29696-2U000</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>87</v>
+        <v>351</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -799,23 +705,17 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>90</v>
-      </c>
-      <c r="E16" t="n">
-        <v>487</v>
-      </c>
-      <c r="F16" t="n">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>28415-08400</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>515</v>
+        <v>88</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -823,23 +723,17 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>237</v>
-      </c>
-      <c r="E17" t="n">
-        <v>386</v>
-      </c>
-      <c r="F17" t="n">
-        <v>288</v>
+        <v>261</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>469</v>
+        <v>126</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -847,23 +741,17 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>348</v>
-      </c>
-      <c r="E18" t="n">
-        <v>473</v>
-      </c>
-      <c r="F18" t="n">
-        <v>451</v>
+        <v>271</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>668</v>
+        <v>208</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -871,23 +759,17 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>325</v>
-      </c>
-      <c r="E19" t="n">
-        <v>319</v>
-      </c>
-      <c r="F19" t="n">
-        <v>165</v>
+        <v>463</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>28415-08400</t>
+          <t>28422-2M100</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>333</v>
+        <v>369</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -895,23 +777,17 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>77</v>
-      </c>
-      <c r="E20" t="n">
-        <v>225</v>
-      </c>
-      <c r="F20" t="n">
-        <v>34</v>
+        <v>372</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>25451-P7200</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>462</v>
+        <v>844</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -919,23 +795,17 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>323</v>
-      </c>
-      <c r="E21" t="n">
-        <v>155</v>
-      </c>
-      <c r="F21" t="n">
-        <v>407</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>28421-2M100</t>
+          <t>29696-2U000</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>615</v>
+        <v>115</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -943,23 +813,17 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>28</v>
-      </c>
-      <c r="E22" t="n">
-        <v>180</v>
-      </c>
-      <c r="F22" t="n">
-        <v>259</v>
+        <v>74</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>28421-2M100</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>327</v>
+        <v>212</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -967,23 +831,17 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>236</v>
-      </c>
-      <c r="E23" t="n">
-        <v>231</v>
-      </c>
-      <c r="F23" t="n">
-        <v>19</v>
+        <v>88</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>29673-2F900</t>
+          <t>A6722031002</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>387</v>
+        <v>166</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -991,13 +849,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>425</v>
-      </c>
-      <c r="E24" t="n">
-        <v>146</v>
-      </c>
-      <c r="F24" t="n">
-        <v>39</v>
+        <v>389</v>
       </c>
     </row>
     <row r="25">
@@ -1007,7 +859,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>894</v>
+        <v>87</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1015,23 +867,17 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>500</v>
-      </c>
-      <c r="E25" t="n">
-        <v>437</v>
-      </c>
-      <c r="F25" t="n">
-        <v>46</v>
+        <v>90</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>618</v>
+        <v>515</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1039,13 +885,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>259</v>
-      </c>
-      <c r="E26" t="n">
-        <v>196</v>
-      </c>
-      <c r="F26" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="27">
@@ -1055,7 +895,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>577</v>
+        <v>788</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1063,23 +903,17 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>488</v>
-      </c>
-      <c r="E27" t="n">
-        <v>405</v>
-      </c>
-      <c r="F27" t="n">
-        <v>378</v>
+        <v>296</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>29673-2F900</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>470</v>
+        <v>707</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1087,23 +921,17 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>465</v>
-      </c>
-      <c r="E28" t="n">
-        <v>414</v>
-      </c>
-      <c r="F28" t="n">
-        <v>292</v>
+        <v>473</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>28415-08400</t>
+          <t>A6722031002</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>202</v>
+        <v>668</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1111,23 +939,17 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>164</v>
-      </c>
-      <c r="E29" t="n">
-        <v>309</v>
-      </c>
-      <c r="F29" t="n">
-        <v>243</v>
+        <v>325</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A6722030900</t>
+          <t>A6722031002</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>164</v>
+        <v>340</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1135,23 +957,17 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>490</v>
-      </c>
-      <c r="E30" t="n">
-        <v>31</v>
-      </c>
-      <c r="F30" t="n">
-        <v>230</v>
+        <v>442</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>840</v>
+        <v>333</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1159,23 +975,17 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>460</v>
-      </c>
-      <c r="E31" t="n">
-        <v>428</v>
-      </c>
-      <c r="F31" t="n">
-        <v>175</v>
+        <v>77</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>28674-L5500</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1183,23 +993,17 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>258</v>
-      </c>
-      <c r="E32" t="n">
-        <v>330</v>
-      </c>
-      <c r="F32" t="n">
-        <v>88</v>
+        <v>240</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>29673-2F900</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>263</v>
+        <v>656</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1207,23 +1011,17 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>362</v>
-      </c>
-      <c r="E33" t="n">
-        <v>224</v>
-      </c>
-      <c r="F33" t="n">
-        <v>224</v>
+        <v>155</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A6722030900</t>
+          <t>28421-2M100</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>545</v>
+        <v>615</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1231,13 +1029,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>312</v>
-      </c>
-      <c r="E34" t="n">
-        <v>81</v>
-      </c>
-      <c r="F34" t="n">
-        <v>186</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35">
@@ -1247,7 +1039,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>949</v>
+        <v>529</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1255,23 +1047,17 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>144</v>
-      </c>
-      <c r="E35" t="n">
-        <v>198</v>
-      </c>
-      <c r="F35" t="n">
-        <v>209</v>
+        <v>37</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>28421-2M100</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>705</v>
+        <v>482</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1279,23 +1065,17 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>306</v>
-      </c>
-      <c r="E36" t="n">
-        <v>26</v>
-      </c>
-      <c r="F36" t="n">
-        <v>404</v>
+        <v>231</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>28415-08400</t>
+          <t>29673-2F900</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>672</v>
+        <v>68</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1303,23 +1083,17 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>171</v>
-      </c>
-      <c r="E37" t="n">
-        <v>33</v>
-      </c>
-      <c r="F37" t="n">
-        <v>168</v>
+        <v>188</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>28421-2M100</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>581</v>
+        <v>88</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1327,23 +1101,17 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>347</v>
-      </c>
-      <c r="E38" t="n">
-        <v>197</v>
-      </c>
-      <c r="F38" t="n">
-        <v>145</v>
+        <v>330</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>28421-2M100</t>
+          <t>29673-2F910</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>751</v>
+        <v>639</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1351,23 +1119,17 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>436</v>
-      </c>
-      <c r="E39" t="n">
-        <v>336</v>
-      </c>
-      <c r="F39" t="n">
-        <v>493</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>904</v>
+        <v>403</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1375,13 +1137,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>76</v>
-      </c>
-      <c r="E40" t="n">
-        <v>170</v>
-      </c>
-      <c r="F40" t="n">
-        <v>41</v>
+        <v>236</v>
       </c>
     </row>
     <row r="41">
@@ -1391,7 +1147,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>689</v>
+        <v>577</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1399,23 +1155,17 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>72</v>
-      </c>
-      <c r="E41" t="n">
-        <v>469</v>
-      </c>
-      <c r="F41" t="n">
-        <v>179</v>
+        <v>488</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>28421-2M100</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1000</v>
+        <v>927</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1423,23 +1173,17 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>335</v>
-      </c>
-      <c r="E42" t="n">
-        <v>357</v>
-      </c>
-      <c r="F42" t="n">
-        <v>339</v>
+        <v>21</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>142</v>
+        <v>940</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1447,23 +1191,17 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>304</v>
-      </c>
-      <c r="E43" t="n">
-        <v>362</v>
-      </c>
-      <c r="F43" t="n">
-        <v>480</v>
+        <v>414</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>A6722031002</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>327</v>
+        <v>677</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1471,13 +1209,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>286</v>
-      </c>
-      <c r="E44" t="n">
-        <v>192</v>
-      </c>
-      <c r="F44" t="n">
-        <v>329</v>
+        <v>96</v>
       </c>
     </row>
     <row r="45">
@@ -1487,7 +1219,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>842</v>
+        <v>629</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1495,23 +1227,17 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>65</v>
-      </c>
-      <c r="E45" t="n">
-        <v>343</v>
-      </c>
-      <c r="F45" t="n">
-        <v>359</v>
+        <v>243</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>28674-L5500</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>711</v>
+        <v>164</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1519,23 +1245,17 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>467</v>
-      </c>
-      <c r="E46" t="n">
-        <v>269</v>
-      </c>
-      <c r="F46" t="n">
-        <v>47</v>
+        <v>490</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>28415-08400</t>
+          <t>29673-2F900</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>696</v>
+        <v>471</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1543,23 +1263,17 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>216</v>
-      </c>
-      <c r="E47" t="n">
-        <v>260</v>
-      </c>
-      <c r="F47" t="n">
-        <v>185</v>
+        <v>52</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>29673-2F900</t>
+          <t>28422-2M100</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>381</v>
+        <v>741</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1567,23 +1281,17 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>158</v>
-      </c>
-      <c r="E48" t="n">
-        <v>92</v>
-      </c>
-      <c r="F48" t="n">
-        <v>486</v>
+        <v>43</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>359</v>
+        <v>671</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1591,23 +1299,17 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>485</v>
-      </c>
-      <c r="E49" t="n">
-        <v>392</v>
-      </c>
-      <c r="F49" t="n">
-        <v>248</v>
+        <v>88</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>29673-2F900</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>241</v>
+        <v>263</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1615,23 +1317,17 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>70</v>
-      </c>
-      <c r="E50" t="n">
-        <v>79</v>
-      </c>
-      <c r="F50" t="n">
-        <v>39</v>
+        <v>362</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>28421-2M100</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>874</v>
+        <v>459</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1639,13 +1335,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>403</v>
-      </c>
-      <c r="E51" t="n">
-        <v>51</v>
-      </c>
-      <c r="F51" t="n">
-        <v>259</v>
+        <v>268</v>
       </c>
     </row>
     <row r="52">
@@ -1655,7 +1345,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>865</v>
+        <v>634</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -1663,23 +1353,17 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>378</v>
-      </c>
-      <c r="E52" t="n">
-        <v>452</v>
-      </c>
-      <c r="F52" t="n">
-        <v>269</v>
+        <v>81</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>29673-2F900</t>
+          <t>28422-2M100</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>687</v>
+        <v>391</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -1687,23 +1371,17 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>172</v>
-      </c>
-      <c r="E53" t="n">
-        <v>448</v>
-      </c>
-      <c r="F53" t="n">
-        <v>392</v>
+        <v>469</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>28421-2M100</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>144</v>
+        <v>406</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -1711,23 +1389,17 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>305</v>
-      </c>
-      <c r="E54" t="n">
-        <v>192</v>
-      </c>
-      <c r="F54" t="n">
-        <v>78</v>
+        <v>209</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>29673-2R060</t>
+          <t>28422-2M100</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>195</v>
+        <v>705</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -1735,23 +1407,17 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>425</v>
-      </c>
-      <c r="E55" t="n">
-        <v>354</v>
-      </c>
-      <c r="F55" t="n">
-        <v>394</v>
+        <v>306</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>29673-2F900</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>838</v>
+        <v>818</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -1759,23 +1425,17 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>462</v>
-      </c>
-      <c r="E56" t="n">
-        <v>84</v>
-      </c>
-      <c r="F56" t="n">
-        <v>369</v>
+        <v>323</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>25451-P7200</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>54</v>
+        <v>352</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -1783,23 +1443,17 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>210</v>
-      </c>
-      <c r="E57" t="n">
-        <v>186</v>
-      </c>
-      <c r="F57" t="n">
-        <v>346</v>
+        <v>33</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>28674-L5500</t>
+          <t>28422-2M100</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>253</v>
+        <v>106</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -1807,23 +1461,17 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>496</v>
-      </c>
-      <c r="E58" t="n">
-        <v>227</v>
-      </c>
-      <c r="F58" t="n">
-        <v>312</v>
+        <v>285</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>28421-2M100</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>780</v>
+        <v>405</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -1831,23 +1479,17 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>383</v>
-      </c>
-      <c r="E59" t="n">
-        <v>401</v>
-      </c>
-      <c r="F59" t="n">
-        <v>229</v>
+        <v>145</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>28421-2M100</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>556</v>
+        <v>751</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -1855,23 +1497,17 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>122</v>
-      </c>
-      <c r="E60" t="n">
-        <v>158</v>
-      </c>
-      <c r="F60" t="n">
-        <v>494</v>
+        <v>436</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>25451-P7200</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>935</v>
+        <v>997</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -1879,13 +1515,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>427</v>
-      </c>
-      <c r="E61" t="n">
-        <v>99</v>
-      </c>
-      <c r="F61" t="n">
-        <v>188</v>
+        <v>464</v>
       </c>
     </row>
   </sheetData>
